--- a/human_validation/judge/kor/judge_D012_S002_P002__qwen3-235b_kor.xlsx
+++ b/human_validation/judge/kor/judge_D012_S002_P002__qwen3-235b_kor.xlsx
@@ -70,16 +70,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -447,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B33"/>
+  <dimension ref="A1:B26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="90" customWidth="1" min="1" max="1"/>
@@ -561,12 +558,82 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>환자 프로필</t>
+          <t>대화문</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사 질문] 안녕하세요, 진료실에 오신 것을 환영합니다. 오늘 어떤 일로 오셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 환자 응답] 다리를 건너야 한다는 걸 알게 되면 갑작스럽고 끔찍한 두려움이 생겨서 왔어요. 다리에 올라가기도 전에 심장이 쿵쾅거리기 시작하고, 운전대나 팔걸이를 잡은 손이 축축해지고, 그냥 두려움에 압도되는 느낌이에요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사의 감별진단] 특정공포증 (D012)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사 질문] 이 두려움은 다리에서만 경험하시는 건가요, 아니면 사람 많은 곳이나 공공장소, 아니면 특별한 이유 없이도 일어나는 다른 상황들이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 환자 응답] 정말 다리 때문이에요. 그냥 사람 많은 곳이나 공공장소에 있다고 해서 똑같은 두려움을 느끼지는 않고, 느닷없이 생기지도 않아요. 그 다리들 위로 매일 수많은 차들이 지나간다는 걸 알고는 있는데, 앞에 높은 다리가 보이거나, 지도에서만 봐도, 마치 그게 우리 밑에서 그냥 무너져 내릴 것 같은 느낌이 들어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사의 감별진단] 특정공포증 (D012)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사 질문] 다리 근처에 있지 않을 때, 터널이나 고층 건물, 엘리베이터 같은 다른 구조물에 대해서도 같은 방식으로 걱정하시는 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 환자 응답] 아니요, 딱히 같은 방식으로는 아니에요. 다리, 특히 높은 다리가 문제예요. 차들이 하루 종일 그 위로 지나다닌다는 걸 머리로는 아는데, 도로에서 다리가 다가오는 게 보이거나 지도에서만 봐도, 그 전체가 우리 밑에서 무너져 내릴 것 같은 느낌이 들어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사의 감별진단] 특정공포증 (D012)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>최종 진단 및 진단 체크리스트</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t>진단명: 특정공포증 (D012)
 인구통계: 성별 남성 / 나이 87 / 직업상태 not in workforce / 최종학력 학사
@@ -575,131 +642,32 @@
 증상 지속 기간: 2 years and 5 months
 추가 요건: 
 주호소 증상 코드: S063
-배경 서술: 제임스의 가까운 브리지 파트너이자 오랜 탐조 동료가 데셉션 패스로 향하는, 그들이 자주 이용하던 높은 다리 구간 근처에서 교통사고로 세상을 떠났다. 그 후 몇 달에 걸쳐 제임스는 다리를 피하려고 심부름 동선을 재조정하기 시작했고, 2년 5개월에 걸쳐 다리를 건너야만 하는 상황이 불가피해질 때마다 즉각적인 두려움이 생겼으며, 이로 인해 산후안 제도 여행을 포기하고 시애틀 극장 나들이를 놓치고, 특정 다리를 건너야 하는 자원봉사 활동을 거절하게 되었다. 이 두려움은 평범한 조심성을 훨씬 넘어서 그의 삶을 좁혔고, 그는 꼭 필요한 다리 건너기조차 극심한 고통과 정교한 사전 계획을 통해서만 견뎌낼 수 있었다. 그는 자신의 독립성이 실제 신체 능력이 아니라 도로 지도에 의해 결정되고 있다고 느껴 1차 진료소에 전화해 도움을 요청한 뒤, 정신과 진료를 받게 되었다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>대화문</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사 질문] 안녕하세요, 진료실에 오신 것을 환영합니다. 오늘 어떤 일로 오셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 환자 응답] 다리를 건너야 한다는 걸 알게 되면 갑작스럽고 끔찍한 두려움이 생겨서 왔어요. 다리에 올라가기도 전에 심장이 쿵쾅거리기 시작하고, 운전대나 팔걸이를 잡은 손이 축축해지고, 그냥 두려움에 압도되는 느낌이에요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사의 감별진단] 중간확률: 특정공포증 (D012)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사 질문] 이 두려움은 다리에서만 경험하시는 건가요, 아니면 사람 많은 곳이나 공공장소, 아니면 특별한 이유 없이도 일어나는 다른 상황들이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 환자 응답] 정말 다리 때문이에요. 그냥 사람 많은 곳이나 공공장소에 있다고 해서 똑같은 두려움을 느끼지는 않고, 느닷없이 생기지도 않아요. 그 다리들 위로 매일 수많은 차들이 지나간다는 걸 알고는 있는데, 앞에 높은 다리가 보이거나, 지도에서만 봐도, 마치 그게 우리 밑에서 그냥 무너져 내릴 것 같은 느낌이 들어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사의 감별진단] 중간확률: 특정공포증 (D012)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사 질문] 다리 근처에 있지 않을 때, 터널이나 고층 건물, 엘리베이터 같은 다른 구조물에 대해서도 같은 방식으로 걱정하시는 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 환자 응답] 아니요, 딱히 같은 방식으로는 아니에요. 다리, 특히 높은 다리가 문제예요. 차들이 하루 종일 그 위로 지나다닌다는 걸 머리로는 아는데, 도로에서 다리가 다가오는 게 보이거나 지도에서만 봐도, 그 전체가 우리 밑에서 무너져 내릴 것 같은 느낌이 들어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
+배경 서술: 제임스의 가까운 브리지 파트너이자 오랜 탐조 동료가 데셉션 패스로 향하는, 그들이 자주 이용하던 높은 다리 구간 근처에서 교통사고로 세상을 떠났다. 그 후 몇 달에 걸쳐 제임스는 다리를 피하려고 심부름 동선을 재조정하기 시작했고, 2년 5개월에 걸쳐 다리를 건너야만 하는 상황이 불가피해질 때마다 즉각적인 두려움이 생겼으며, 이로 인해 산후안 제도 여행을 포기하고 시애틀 극장 나들이를 놓치고, 특정 다리를 건너야 하는 자원봉사 활동을 거절하게 되었다. 이 두려움은 평범한 조심성을 훨씬 넘어서 그의 삶을 좁혔고, 그는 꼭 필요한 다리 건너기조차 극심한 고통과 정교한 사전 계획을 통해서만 견뎌낼 수 있었다. 그는 자신의 독립성이 실제 신체 능력이 아니라 도로 지도에 의해 결정되고 있다고 느껴 1차 진료소에 전화해 도움을 요청한 뒤, 정신과 진료를 받게 되었다.
+표집된 증상 목록:
+  - S062 특정 공포 대상에 대한 두려움: 실제 위험에 비해 지나치게 강한, 특정 대상이나 상황에 대한 뚜렷한 두려움이나 불안(아동의 경우 울음, 떼쓰기, 얼어붙음, 매달림으로 표현될 수 있음).
+  - S063 즉각적 공포/불안 반응: 공포 대상이나 상황에 노출되면 거의 항상 즉각적인 두려움이나 불안이 유발됨.
+  - S064 공포 대상 회피/견딤: 공포 대상이나 상황을 적극적으로 회피하거나 강한 두려움·불안을 견디며 버팀.</t>
+        </is>
+      </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>[3번째 턴 · 의사의 감별진단] 중간확률: 특정공포증 (D012)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>최종 진단 및 진단 체크리스트</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="6" t="inlineStr">
-        <is>
-          <t>의사의 최종 진단: 특정공포증 (D012, ICD: F40.2)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="5" t="inlineStr">
-        <is>
-          <t>지속 기간 요건 — 점수: 0.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>기능적 손상 요건 — 점수: 1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="5" t="inlineStr">
-        <is>
-          <t>추가 요건 — 점수: None</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: phobic_symptoms (관계=must_include, 요구개수=3, 충족개수=2, 커버리지=0.6667)
-  확인된 근거: 특정 공포 대상에 대한 두려움: 실제 위험에 비해 지나치게 강한, 특정 대상이나 상황에 대한 뚜렷한 두려움이나 불안(아동의 경우 울음, 떼쓰기, 얼어붙음, 매달림으로 표현될 수 있음).; 즉각적 공포/불안 반응: 공포 대상이나 상황에 노출되면 거의 항상 즉각적인 두려움이나 불안이 유발됨.
-  누락: 공포 대상 회피/견딤: 공포 대상이나 상황을 적극적으로 회피하거나 강한 두려움·불안을 견디며 버팀.</t>
+          <t>의사의 최종 진단: 특정공포증 (D012, ICD: F40.2)
+지속 기간 요건: 없음
+기능적 손상 요건: 있음
+추가 요건: None
+체크리스트 그룹: phobic_symptoms (관계=must_include, 요구개수=3, 충족개수=2, 커버리지=0.6667)
+확인된 근거:
+  - 특정 공포 대상에 대한 두려움: 실제 위험에 비해 지나치게 강한, 특정 대상이나 상황에 대한 뚜렷한 두려움이나 불안(아동의 경우 울음, 떼쓰기, 얼어붙음, 매달림으로 표현될 수 있음).
+  - 즉각적 공포/불안 반응: 공포 대상이나 상황에 노출되면 거의 항상 즉각적인 두려움이나 불안이 유발됨.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="4">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A25:B25"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D012_S002_P002__qwen3-235b_kor.xlsx
+++ b/human_validation/judge/kor/judge_D012_S002_P002__qwen3-235b_kor.xlsx
@@ -628,6 +628,11 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>환자 증상 프로필</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>최종 진단 및 진단 체크리스트</t>
         </is>
       </c>
@@ -663,11 +668,10 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="3">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A25:B25"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D012_S002_P002__qwen3-235b_kor.xlsx
+++ b/human_validation/judge/kor/judge_D012_S002_P002__qwen3-235b_kor.xlsx
@@ -458,6 +458,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -502,7 +503,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="8">
@@ -555,6 +556,7 @@
         <v>0.3333</v>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
